--- a/selenium_model/LOAD_TESTING_350_REPORT.xlsx
+++ b/selenium_model/LOAD_TESTING_350_REPORT.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -3463,7 +3463,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F87" t="n">
@@ -3883,7 +3883,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F99" t="n">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F107" t="n">
@@ -4653,7 +4653,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F121" t="n">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F168" t="n">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F185" t="n">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F187" t="n">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F198" t="n">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F203" t="n">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F226" t="n">
@@ -8713,7 +8713,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F237" t="n">
@@ -8783,7 +8783,7 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F239" t="n">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F258" t="n">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F282" t="n">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F314" t="n">
@@ -11583,7 +11583,7 @@
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F319" t="n">
@@ -12248,7 +12248,7 @@
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F338" t="n">
@@ -12388,7 +12388,7 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="F342" t="n">
